--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟠 賠率0.56&lt;1 應出場</t>
+          <t>🟠 賠率0.65&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>115.5</v>
+        <v>116.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43.2</v>
+        <v>43.5</v>
       </c>
       <c r="E4" t="n">
         <v>43.99</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.82&lt;1 應出場</t>
+          <t>🟠 賠率0.60&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價72.3)</t>
+          <t>🔴 跌破停損價540(現價72.9)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>277.5</v>
+        <v>277</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -856,7 +856,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價277.5)</t>
+          <t>🔴 跌破停損價300(現價277.0)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E8" t="n">
         <v>190.02</v>
@@ -996,7 +996,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率3.23 持有</t>
+          <t>🟢 賠率3.58 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>164.5</v>
+        <v>163</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率2.18 持有</t>
+          <t>🟢 賠率2.38 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>119</v>
+        <v>118.5</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟠 賠率0.65&lt;1 應出場</t>
+          <t>🟠 賠率0.70&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>116.5</v>
+        <v>115</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.38&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -669,12 +669,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43.5</v>
+        <v>274</v>
       </c>
       <c r="E4" t="n">
-        <v>43.99</v>
+        <v>305.63</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>340</v>
       </c>
       <c r="G4" t="n">
-        <v>41</v>
+        <v>300</v>
       </c>
       <c r="H4" t="n">
-        <v>34.9</v>
+        <v>244.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -703,24 +703,24 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>36</v>
+        <v>166.7</v>
       </c>
       <c r="K4" t="n">
-        <v>34.9</v>
+        <v>244.6</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>145.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.60&lt;1 應出場</t>
+          <t>🔴 跌破停損價300(現價274.0)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -730,7 +730,11 @@
           <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -749,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價72.9)</t>
+          <t>🔴 跌破停損價540(現價73.0)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -805,72 +809,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔴 出場</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>277</v>
+        <v>176.5</v>
       </c>
       <c r="E6" t="n">
-        <v>305.63</v>
+        <v>190.02</v>
       </c>
       <c r="F6" t="n">
-        <v>340</v>
+        <v>220</v>
       </c>
       <c r="G6" t="n">
-        <v>300</v>
+        <v>165</v>
       </c>
       <c r="H6" t="n">
-        <v>244.6</v>
+        <v>194</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>166.7</v>
+        <v>194</v>
       </c>
       <c r="K6" t="n">
-        <v>244.6</v>
+        <v>158.8</v>
       </c>
       <c r="L6" t="n">
-        <v>145.3</v>
+        <v>235.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價277.0)</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>🟢 賠率3.78 持有</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(10.8→10.4→9.3)</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>216.5</v>
+        <v>215.5</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟢 賠率2.03 持有</t>
+          <t>🟢 賠率2.23 持有</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -945,12 +945,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -959,53 +959,53 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>177</v>
+        <v>42.8</v>
       </c>
       <c r="E8" t="n">
-        <v>190.02</v>
+        <v>43.99</v>
       </c>
       <c r="F8" t="n">
-        <v>220</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>165</v>
+        <v>41</v>
       </c>
       <c r="H8" t="n">
-        <v>194</v>
+        <v>34.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>194</v>
+        <v>36</v>
       </c>
       <c r="K8" t="n">
-        <v>158.8</v>
+        <v>34.9</v>
       </c>
       <c r="L8" t="n">
-        <v>235.2</v>
+        <v>36</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率3.58 持有</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(10.8→10.4→9.3)</t>
-        </is>
-      </c>
+          <t>🟡 賠率1.22 考慮減碼</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
       <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率2.38 持有</t>
+          <t>🟢 賠率3.26 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -533,33 +533,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🔴 出場</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>118.5</v>
-      </c>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>117.63</v>
+        <v>236.26</v>
       </c>
       <c r="F2" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="G2" t="n">
-        <v>102</v>
+        <v>200</v>
       </c>
       <c r="H2" t="n">
-        <v>102</v>
+        <v>252.6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -567,104 +565,94 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>102</v>
+        <v>252.6</v>
       </c>
       <c r="K2" t="n">
-        <v>87.59999999999999</v>
+        <v>292</v>
       </c>
       <c r="L2" t="n">
-        <v>105.9</v>
+        <v>232.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 200 太鬆(財報支撐在 253,低 21%)→ 多賠</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>🟠 賠率0.70&lt;1 應出場</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>🟡 最新月YoY-11.6%轉負</t>
-        </is>
-      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>🟢 現價下不會買(非A/B級)</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>🟠 負債比81% &gt; 70% 且流動比83% &lt; 100%(短期償債警報)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔴 出場</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>115</v>
-      </c>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>111.6</v>
+        <v>636</v>
       </c>
       <c r="F3" t="n">
-        <v>130</v>
+        <v>720</v>
       </c>
       <c r="G3" t="n">
-        <v>76</v>
+        <v>540</v>
       </c>
       <c r="H3" t="n">
-        <v>76.59999999999999</v>
+        <v>569.4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>92.40000000000001</v>
+        <v>569.4</v>
       </c>
       <c r="K3" t="n">
-        <v>76.59999999999999</v>
+        <v>526.2</v>
       </c>
       <c r="L3" t="n">
-        <v>100.4</v>
+        <v>559.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 540 太鬆(財報支撐在 569,低 5%)→ 多賠</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>🔴 賠率0.38&lt;0.5 立刻賣</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>🟠 負債比80% &gt; 80%(高槓桿)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -679,12 +667,10 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔴 出場</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>274</v>
-      </c>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>305.63</v>
       </c>
@@ -718,16 +704,12 @@
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>🔴 跌破停損價300(現價274.0)</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級)</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -739,103 +721,91 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔴 出場</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>73</v>
-      </c>
+          <t>🟡 警戒</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>636</v>
+        <v>43.99</v>
       </c>
       <c r="F5" t="n">
-        <v>720</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>540</v>
+        <v>41</v>
       </c>
       <c r="H5" t="n">
-        <v>569.4</v>
+        <v>34.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>569.4</v>
+        <v>36</v>
       </c>
       <c r="K5" t="n">
-        <v>526.2</v>
+        <v>34.9</v>
       </c>
       <c r="L5" t="n">
-        <v>559.2</v>
+        <v>36</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 540 太鬆(財報支撐在 569,低 5%)→ 多賠</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>🔴 跌破停損價540(現價73.0)</t>
-        </is>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>🟠 負債比80% &gt; 80%(高槓桿)</t>
-        </is>
-      </c>
+          <t>🟢 現價下不會買(非A/B級)</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>176.5</v>
-      </c>
+          <t>🟢 抱緊</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>190.02</v>
+        <v>117.63</v>
       </c>
       <c r="F6" t="n">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="G6" t="n">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="H6" t="n">
-        <v>194</v>
+        <v>102</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -843,31 +813,23 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>194</v>
+        <v>102</v>
       </c>
       <c r="K6" t="n">
-        <v>158.8</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>235.2</v>
+        <v>105.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>🟢 賠率3.78 持有</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(10.8→10.4→9.3)</t>
-        </is>
-      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -875,137 +837,113 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>215.5</v>
-      </c>
+          <t>🟢 抱緊</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>236.26</v>
+        <v>111.6</v>
       </c>
       <c r="F7" t="n">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="G7" t="n">
-        <v>200</v>
+        <v>76</v>
       </c>
       <c r="H7" t="n">
-        <v>252.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>252.6</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>292</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>232.2</v>
+        <v>100.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 200 太鬆(財報支撐在 253,低 21%)→ 多賠</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>🟢 賠率2.23 持有</t>
-        </is>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>🟢 現價下不會買(非A/B級)</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>🟠 負債比81% &gt; 70% 且流動比83% &lt; 100%(短期償債警報)</t>
-        </is>
-      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>42.8</v>
-      </c>
+          <t>🟢 抱緊</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>43.99</v>
+        <v>190.02</v>
       </c>
       <c r="F8" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="G8" t="n">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="H8" t="n">
-        <v>34.9</v>
+        <v>194</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>36</v>
+        <v>194</v>
       </c>
       <c r="K8" t="n">
-        <v>34.9</v>
+        <v>158.8</v>
       </c>
       <c r="L8" t="n">
-        <v>36</v>
+        <v>235.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>🟡 賠率1.22 考慮減碼</t>
-        </is>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1024,9 +962,7 @@
           <t>🟢 抱緊</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>158</v>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>160.86</v>
       </c>
@@ -1060,11 +996,7 @@
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>🟢 賠率3.26 持有</t>
-        </is>
-      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -533,31 +533,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>🔴 出場</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>119.5</v>
+      </c>
       <c r="E2" t="n">
-        <v>236.26</v>
+        <v>117.63</v>
       </c>
       <c r="F2" t="n">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="G2" t="n">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="H2" t="n">
-        <v>252.6</v>
+        <v>102</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -565,123 +567,135 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>252.6</v>
+        <v>102</v>
       </c>
       <c r="K2" t="n">
-        <v>292</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>232.2</v>
+        <v>105.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 200 太鬆(財報支撐在 253,低 21%)→ 多賠</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>🟠 賠率0.60&lt;1 應出場</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>🟡 最新月YoY-11.6%轉負</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級)</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>🟠 負債比81% &gt; 70% 且流動比83% &lt; 100%(短期償債警報)</t>
-        </is>
-      </c>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>🔴 出場</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>118.5</v>
+      </c>
       <c r="E3" t="n">
-        <v>636</v>
+        <v>111.6</v>
       </c>
       <c r="F3" t="n">
-        <v>720</v>
+        <v>130</v>
       </c>
       <c r="G3" t="n">
-        <v>540</v>
+        <v>76</v>
       </c>
       <c r="H3" t="n">
-        <v>569.4</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>569.4</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>526.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>559.2</v>
+        <v>100.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 540 太鬆(財報支撐在 569,低 5%)→ 多賠</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>🔴 賠率0.27&lt;0.5 立刻賣</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>🟠 負債比80% &gt; 80%(高槓桿)</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>🔴 出場</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>43.2</v>
+      </c>
       <c r="E4" t="n">
-        <v>305.63</v>
+        <v>43.99</v>
       </c>
       <c r="F4" t="n">
-        <v>340</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>300</v>
+        <v>41</v>
       </c>
       <c r="H4" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -689,206 +703,244 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>166.7</v>
+        <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="L4" t="n">
-        <v>145.3</v>
+        <v>36</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟠 賠率0.82&lt;1 應出場</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級)</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🟡 警戒</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>🔴 出場</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>72.09999999999999</v>
+      </c>
       <c r="E5" t="n">
-        <v>43.99</v>
+        <v>636</v>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>720</v>
       </c>
       <c r="G5" t="n">
-        <v>41</v>
+        <v>540</v>
       </c>
       <c r="H5" t="n">
-        <v>34.9</v>
+        <v>569.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>36</v>
+        <v>569.4</v>
       </c>
       <c r="K5" t="n">
-        <v>34.9</v>
+        <v>526.2</v>
       </c>
       <c r="L5" t="n">
-        <v>36</v>
+        <v>559.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 540 太鬆(財報支撐在 569,低 5%)→ 多賠</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>🔴 跌破停損價540(現價72.1)</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級)</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>🟠 負債比80% &gt; 80%(高槓桿)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🟢 抱緊</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>🔴 出場</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>281</v>
+      </c>
       <c r="E6" t="n">
-        <v>117.63</v>
+        <v>305.63</v>
       </c>
       <c r="F6" t="n">
-        <v>130</v>
+        <v>340</v>
       </c>
       <c r="G6" t="n">
-        <v>102</v>
+        <v>300</v>
       </c>
       <c r="H6" t="n">
-        <v>102</v>
+        <v>244.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>102</v>
+        <v>166.7</v>
       </c>
       <c r="K6" t="n">
-        <v>87.59999999999999</v>
+        <v>244.6</v>
       </c>
       <c r="L6" t="n">
-        <v>105.9</v>
+        <v>145.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>🔴 跌破停損價300(現價281.0)</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🟢 抱緊</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>216.5</v>
+      </c>
       <c r="E7" t="n">
-        <v>111.6</v>
+        <v>236.26</v>
       </c>
       <c r="F7" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="G7" t="n">
-        <v>76</v>
+        <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>76.59999999999999</v>
+        <v>252.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>92.40000000000001</v>
+        <v>252.6</v>
       </c>
       <c r="K7" t="n">
-        <v>76.59999999999999</v>
+        <v>292</v>
       </c>
       <c r="L7" t="n">
-        <v>100.4</v>
+        <v>232.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 200 太鬆(財報支撐在 253,低 21%)→ 多賠</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>🟢 賠率2.03 持有</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(非A/B級)</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>🟠 負債比81% &gt; 70% 且流動比83% &lt; 100%(短期償債警報)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -903,10 +955,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🟢 抱緊</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>180</v>
+      </c>
       <c r="E8" t="n">
         <v>190.02</v>
       </c>
@@ -940,8 +994,16 @@
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>🟢 賠率2.67 持有</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(10.8→10.4→9.3)</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -959,10 +1021,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🟢 抱緊</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>167</v>
+      </c>
       <c r="E9" t="n">
         <v>160.86</v>
       </c>
@@ -996,10 +1060,18 @@
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>🟡 賠率1.89 考慮減碼</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr"/>
     </row>
   </sheetData>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>119.5</v>
+        <v>119</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟠 賠率0.60&lt;1 應出場</t>
+          <t>🟠 賠率0.65&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>118.5</v>
+        <v>119</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.27&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.26&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="E4" t="n">
         <v>43.99</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.82&lt;1 應出場</t>
+          <t>🟠 賠率0.90&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價72.1)</t>
+          <t>🔴 跌破停損價540(現價71.3)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>281</v>
+        <v>281.5</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -856,7 +856,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價281.0)</t>
+          <t>🔴 跌破停損價300(現價281.5)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>216.5</v>
+        <v>215</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟢 賠率2.03 持有</t>
+          <t>🟢 賠率2.33 持有</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>180</v>
+        <v>179.5</v>
       </c>
       <c r="E8" t="n">
         <v>190.02</v>
@@ -996,7 +996,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率2.67 持有</t>
+          <t>🟢 賠率2.79 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>167</v>
+        <v>166.5</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 賠率1.89 考慮減碼</t>
+          <t>🟡 賠率1.95 考慮減碼</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟠 賠率0.65&lt;1 應出場</t>
+          <t>🟠 賠率0.75&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>119</v>
+        <v>118.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.26&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.27&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -669,12 +669,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43.1</v>
+        <v>282</v>
       </c>
       <c r="E4" t="n">
-        <v>43.99</v>
+        <v>305.63</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>340</v>
       </c>
       <c r="G4" t="n">
-        <v>41</v>
+        <v>300</v>
       </c>
       <c r="H4" t="n">
-        <v>34.9</v>
+        <v>244.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -703,24 +703,24 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>36</v>
+        <v>166.7</v>
       </c>
       <c r="K4" t="n">
-        <v>34.9</v>
+        <v>244.6</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>145.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.90&lt;1 應出場</t>
+          <t>🔴 跌破停損價300(現價282.0)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -730,7 +730,11 @@
           <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -749,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>71.3</v>
+        <v>70.7</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價71.3)</t>
+          <t>🔴 跌破停損價540(現價70.7)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -805,72 +809,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔴 出場</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>281.5</v>
+        <v>181</v>
       </c>
       <c r="E6" t="n">
-        <v>305.63</v>
+        <v>190.02</v>
       </c>
       <c r="F6" t="n">
-        <v>340</v>
+        <v>220</v>
       </c>
       <c r="G6" t="n">
-        <v>300</v>
+        <v>165</v>
       </c>
       <c r="H6" t="n">
-        <v>244.6</v>
+        <v>194</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>166.7</v>
+        <v>194</v>
       </c>
       <c r="K6" t="n">
-        <v>244.6</v>
+        <v>158.8</v>
       </c>
       <c r="L6" t="n">
-        <v>145.3</v>
+        <v>235.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價281.5)</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>🟢 賠率2.44 持有</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(10.8→10.4→9.3)</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟢 賠率2.33 持有</t>
+          <t>🟢 賠率2.57 持有</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -945,12 +945,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -959,19 +959,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>179.5</v>
+        <v>167</v>
       </c>
       <c r="E8" t="n">
-        <v>190.02</v>
+        <v>160.86</v>
       </c>
       <c r="F8" t="n">
         <v>220</v>
       </c>
       <c r="G8" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="H8" t="n">
-        <v>194</v>
+        <v>138.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -979,44 +979,44 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>194</v>
+        <v>138.9</v>
       </c>
       <c r="K8" t="n">
-        <v>158.8</v>
+        <v>113</v>
       </c>
       <c r="L8" t="n">
-        <v>235.2</v>
+        <v>123</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率2.79 持有</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(10.8→10.4→9.3)</t>
-        </is>
-      </c>
+          <t>🟡 賠率1.89 考慮減碼</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
+        </is>
+      </c>
       <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1025,51 +1025,51 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>166.5</v>
+        <v>43</v>
       </c>
       <c r="E9" t="n">
-        <v>160.86</v>
+        <v>43.99</v>
       </c>
       <c r="F9" t="n">
-        <v>220</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>139</v>
+        <v>41</v>
       </c>
       <c r="H9" t="n">
-        <v>138.9</v>
+        <v>34.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>138.9</v>
+        <v>36</v>
       </c>
       <c r="K9" t="n">
-        <v>113</v>
+        <v>34.9</v>
       </c>
       <c r="L9" t="n">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 賠率1.95 考慮減碼</t>
+          <t>🟡 賠率1.00 考慮減碼</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>118.5</v>
+        <v>117.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.27&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.30&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>282</v>
+        <v>281.5</v>
       </c>
       <c r="E4" t="n">
         <v>305.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價282.0)</t>
+          <t>🔴 跌破停損價300(現價281.5)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -790,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價70.7)</t>
+          <t>🔴 跌破停損價540(現價70.8)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E6" t="n">
         <v>190.02</v>
@@ -860,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟢 賠率2.44 持有</t>
+          <t>🟢 賠率2.67 持有</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟢 賠率2.57 持有</t>
+          <t>🟢 賠率2.85 持有</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -945,12 +945,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -959,51 +959,51 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>167</v>
+        <v>42.7</v>
       </c>
       <c r="E8" t="n">
-        <v>160.86</v>
+        <v>43.99</v>
       </c>
       <c r="F8" t="n">
-        <v>220</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>139</v>
+        <v>41</v>
       </c>
       <c r="H8" t="n">
-        <v>138.9</v>
+        <v>34.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>138.9</v>
+        <v>36</v>
       </c>
       <c r="K8" t="n">
-        <v>113</v>
+        <v>34.9</v>
       </c>
       <c r="L8" t="n">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.89 考慮減碼</t>
+          <t>🟡 賠率1.35 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1011,67 +1011,63 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟢 抱緊</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="E9" t="n">
-        <v>43.99</v>
+        <v>160.86</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="G9" t="n">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="H9" t="n">
-        <v>34.9</v>
+        <v>138.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>36</v>
+        <v>138.9</v>
       </c>
       <c r="K9" t="n">
-        <v>34.9</v>
+        <v>113</v>
       </c>
       <c r="L9" t="n">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 賠率1.00 考慮減碼</t>
+          <t>🟢 賠率2.38 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
     </row>
   </sheetData>
